--- a/ksoft_old/docs/stock/Bestand_Finish_Folie_Set_up_details.xlsx
+++ b/ksoft_old/docs/stock/Bestand_Finish_Folie_Set_up_details.xlsx
@@ -11699,13 +11699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74A0AE8B-739F-46F3-BBC5-AA845E2B952B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF2EDF-2504-4A75-9DE4-069F75D7FA2B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E84D56B-E7F3-4BE0-8413-5C40F879D9F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88CA8D7E-8FB7-469E-80F3-3E6DDDFFA615}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA0B7BAC-A8BF-4705-BDC4-B4D1213C650F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{703EACC6-9D8A-4734-9631-587EB7614AA7}"/>
 </file>
--- a/ksoft_old/docs/stock/Bestand_Finish_Folie_Set_up_details.xlsx
+++ b/ksoft_old/docs/stock/Bestand_Finish_Folie_Set_up_details.xlsx
@@ -11699,13 +11699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF2EDF-2504-4A75-9DE4-069F75D7FA2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61261368-AC41-49D3-BF91-00C79A8082E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88CA8D7E-8FB7-469E-80F3-3E6DDDFFA615}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2D1FEA-2DEC-4438-B0C3-A292E6975057}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{703EACC6-9D8A-4734-9631-587EB7614AA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A454D25-9145-41DF-831A-5CA054997269}"/>
 </file>
--- a/ksoft_old/docs/stock/Bestand_Finish_Folie_Set_up_details.xlsx
+++ b/ksoft_old/docs/stock/Bestand_Finish_Folie_Set_up_details.xlsx
@@ -11699,13 +11699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61261368-AC41-49D3-BF91-00C79A8082E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74A0AE8B-739F-46F3-BBC5-AA845E2B952B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2D1FEA-2DEC-4438-B0C3-A292E6975057}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E84D56B-E7F3-4BE0-8413-5C40F879D9F6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A454D25-9145-41DF-831A-5CA054997269}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA0B7BAC-A8BF-4705-BDC4-B4D1213C650F}"/>
 </file>